--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -505,6 +505,34 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>arch backdrop stand and cover set</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>$56.00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -533,6 +533,34 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>round metal raised garden bed</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>$55.80</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41.3%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,34 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>modofo electric pruning shears</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>$64.93</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -589,6 +589,34 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>trellis arch outdoor</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>$64.86</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -617,6 +617,34 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>outdoor cooking table</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>$90.72</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>73.3%</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -645,6 +645,34 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>lawn edgers battery powered ego</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>$124.12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -673,6 +673,34 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ego lawn edger without battery</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>$136.24</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -701,6 +701,34 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>baby gym set foam</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>$89.03</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46.6%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -729,6 +729,34 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>bookshelf speaker stands adjustable</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>$78.33</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -757,6 +757,34 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>outdoor cooking station with storage</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>$153.53</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -785,6 +785,34 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger cordless ryobi</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>$123.34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -813,6 +813,34 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>hp tuners credits</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>$312.74</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -841,6 +841,34 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>cordless battery lawn edger blade</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$107.82</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -869,6 +869,34 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>360 camera mount for car</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$75.37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -897,6 +897,34 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>belkin 3 in 1 wireless charging station apple</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>$89.51</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>86.7%</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -925,6 +925,34 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>recycling bin outdoor with wheels</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>$82.36</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -953,6 +953,34 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>car mattress for suv back seat</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>$57.18</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -981,6 +981,34 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger tool gas</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>$113.51</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1009,6 +1009,34 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>dewalt lawn edger 60v</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>$122.27</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1037,6 +1037,34 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>gas grills for outdoor cooking with griddle</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>$141.54</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1065,6 +1065,34 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger tool dewalt</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>$105.56</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1093,6 +1093,34 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>getlay garden fence animal barrier</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>$78.48</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>44.7%</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1121,6 +1121,34 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>lawn edgers battery powered 80v</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>$130.99</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1149,6 +1149,34 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>metal garden trellises durable</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>$42.83</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1177,6 +1177,34 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>recycling bin outdoor 32 gallon</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>$75.32</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1205,6 +1205,34 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>car mattress for suv backseat</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>$62.80</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1233,6 +1233,34 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>arched trellis for raised garden bed</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>$42.34</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>53.2%</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1261,6 +1261,34 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ryobi lawn edgers battery powered</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>$124.31</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1289,6 +1289,34 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>dewalt lawn edger and trencher</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>$101.34</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>73.3%</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1317,6 +1317,34 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>charging station for apple devices with clock</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>$43.32</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1345,6 +1345,34 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>gas grills for outdoor cooking</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>$179.46</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1373,6 +1373,34 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>round raised garden beds wood</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>$52.41</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>40.9%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1401,6 +1401,34 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>veradek outdoor planter large</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>$111.07</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1429,6 +1429,34 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>lawn edgers gas powered</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>$123.86</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1457,6 +1457,34 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger tool battery</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>$124.73</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1485,6 +1485,34 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>trellis for climbing plants outdoor 8ft</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>$52.79</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1513,6 +1513,34 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>anker charging station travel</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>$58.62</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1541,6 +1541,34 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>dewalt lawn edger</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>$101.70</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1569,6 +1569,34 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>car mattress for suv kids</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>$52.24</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1597,6 +1597,34 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>travel adapter and voltage converter for italy</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>$32.44</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1625,6 +1625,34 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>fish fryers outdoor cooking with basket</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>$83.38</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>59.1%</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1653,6 +1653,34 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>arc backdrop stand with cover</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>$52.12</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1681,6 +1681,34 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>photo backdrop stand arch</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>$40.74</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1709,6 +1709,34 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>infant pulse oximeter sock</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>$117.66</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1737,6 +1737,34 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>arch backdrop stand and cover set of 3</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>$68.88</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1765,6 +1765,34 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>hp tuners mpvi3 pro</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>$216.14</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1793,6 +1793,34 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>arch backdrop stand heavy duty</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>$61.63</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1821,6 +1821,34 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>arch backdrop stand with cover</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>$50.34</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1849,6 +1849,34 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger cordless dewalt</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>$100.22</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1877,6 +1877,34 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>garage pegboard organizer wood</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>$53.56</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>40.9%</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1905,6 +1905,34 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>lawn edgers battery powered metal blade</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>$102.35</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1933,6 +1933,34 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>arch backdrop stand set of 2</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>$42.71</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1961,6 +1961,34 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>travel adapter and voltage converter korea</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>$33.67</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1989,6 +1989,34 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>fish fryers outdoor cooking</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>$164.31</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2017,6 +2017,34 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>fish fryers outdoor cooking 20qt</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>$93.06</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2045,34 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>outdoor cooking table tall</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>$80.87</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2073,34 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>travel adapter and voltage converter france</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>$34.49</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2101,6 +2101,34 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>first aid kits for businesses osha approved 2025 refills</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>$43.99</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2129,6 +2129,34 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger cordless 40v</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>$121.49</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>57.9%</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2157,34 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>backdrop stand with cover</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>$51.63</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2185,6 +2185,34 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>lawn edgers battery powered with blade</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>$116.90</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2213,6 +2213,34 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>epicka universal travel adapter ta-105c</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>$42.20</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2241,34 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>trellis arch for climbing plants outdoor</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>$49.81</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2269,6 +2269,34 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>fenix headlamp hm65r</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>$90.80</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2297,6 +2297,34 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>outdoor cooking station table</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>$95.06</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2325,6 +2325,34 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>electric pruning shears cordless milwaukee</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>$95.75</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2353,6 +2353,34 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger cordless with blade</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>$109.14</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2381,6 +2381,34 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>arch backdrop stand set of 3</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>$58.82</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>86.4%</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2409,6 +2409,34 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger tool gas powered</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>$94.42</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>42.1%</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-04.xlsx
+++ b/output/amazon_niche_rapor_2026-04-04.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2437,6 +2437,34 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>arch backdrop stand with cover set</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>$54.77</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
